--- a/ig/DM_FINESS_New/CodeSystem-tre-r387-type-groupement-structure.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r387-type-groupement-structure.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/example/CodeSystem/tre-r387-type-groupement-structure</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r387-type-groupement-structure</t>
   </si>
   <si>
     <t>Identifier</t>
